--- a/docs/vendors/chemito/PMIDTC_CIPLAPIS.xlsx
+++ b/docs/vendors/chemito/PMIDTC_CIPLAPIS.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energygna-my.sharepoint.com/personal/raman_sharma_gna_energy/Documents/Desktop/BMS2/BMS/docs/vendors/chemito/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="11_25535FFD175E6FCFCB3D45214BAC33A9CAE27E25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14D7A69-8B06-4C34-9559-50EA4CAF0528}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -837,15 +840,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1437,10 +1440,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C242"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="255.75" customWidth="1"/>
+    <col min="2" max="2" width="255.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1448,18 +1451,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24">
+    <row r="3" spans="1:2" ht="23.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
-    </row>
-    <row r="5" spans="1:2" ht="15.75">
+      <c r="B4" s="18"/>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75">
+    <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1483,8 +1486,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:2" ht="18">
+      <c r="A8" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1492,113 +1495,113 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="18"/>
+      <c r="A9" s="17"/>
       <c r="B9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75">
-      <c r="A10" s="18"/>
+    <row r="10" spans="1:2">
+      <c r="A10" s="17"/>
       <c r="B10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18.75">
-      <c r="A11" s="18"/>
+    <row r="11" spans="1:2" ht="18">
+      <c r="A11" s="17"/>
       <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75">
-      <c r="A13" s="18"/>
+    <row r="13" spans="1:2">
+      <c r="A13" s="17"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18.75">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:2" ht="18">
+      <c r="A14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75">
-      <c r="A15" s="18"/>
+    <row r="15" spans="1:2" ht="18">
+      <c r="A15" s="17"/>
       <c r="B15" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75">
-      <c r="A16" s="18"/>
+    <row r="16" spans="1:2">
+      <c r="A16" s="17"/>
       <c r="B16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75">
-      <c r="A17" s="18"/>
+    <row r="17" spans="1:2">
+      <c r="A17" s="17"/>
       <c r="B17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18.75">
-      <c r="A18" s="18"/>
+    <row r="18" spans="1:2" ht="18">
+      <c r="A18" s="17"/>
       <c r="B18" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75">
-      <c r="A19" s="18"/>
+    <row r="19" spans="1:2">
+      <c r="A19" s="17"/>
       <c r="B19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18.75">
-      <c r="A20" s="18"/>
+    <row r="20" spans="1:2" ht="18">
+      <c r="A20" s="17"/>
       <c r="B20" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75">
-      <c r="A21" s="18" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75">
-      <c r="A22" s="18"/>
+    <row r="22" spans="1:2">
+      <c r="A22" s="17"/>
       <c r="B22" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75">
-      <c r="A23" s="18"/>
+    <row r="23" spans="1:2">
+      <c r="A23" s="17"/>
       <c r="B23" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24">
+    <row r="24" spans="1:2" ht="23.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75">
-      <c r="A25" s="16" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="16"/>
-    </row>
-    <row r="26" spans="1:2" ht="15.75">
+      <c r="B25" s="18"/>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1609,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75">
+    <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
@@ -1614,7 +1617,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75">
+    <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -1622,270 +1625,270 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="18.75">
-      <c r="A29" s="18" t="s">
+    <row r="29" spans="1:2" ht="18">
+      <c r="A29" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75">
-      <c r="A30" s="18"/>
+    <row r="30" spans="1:2">
+      <c r="A30" s="17"/>
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75">
-      <c r="A31" s="18"/>
+    <row r="31" spans="1:2">
+      <c r="A31" s="17"/>
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75">
-      <c r="A32" s="18"/>
+    <row r="32" spans="1:2">
+      <c r="A32" s="17"/>
       <c r="B32" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75">
-      <c r="A33" s="18"/>
+    <row r="33" spans="1:2">
+      <c r="A33" s="17"/>
       <c r="B33" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="18.75">
-      <c r="A34" s="18"/>
+    <row r="34" spans="1:2" ht="18">
+      <c r="A34" s="17"/>
       <c r="B34" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75">
-      <c r="A35" s="18" t="s">
+    <row r="35" spans="1:2">
+      <c r="A35" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75">
-      <c r="A36" s="18"/>
+    <row r="36" spans="1:2">
+      <c r="A36" s="17"/>
       <c r="B36" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75">
-      <c r="A37" s="18"/>
+    <row r="37" spans="1:2">
+      <c r="A37" s="17"/>
       <c r="B37" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75">
-      <c r="A38" s="18"/>
+    <row r="38" spans="1:2">
+      <c r="A38" s="17"/>
       <c r="B38" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="18.75">
-      <c r="A39" s="18" t="s">
+    <row r="39" spans="1:2" ht="18">
+      <c r="A39" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="18.75">
-      <c r="A40" s="18"/>
+    <row r="40" spans="1:2" ht="18">
+      <c r="A40" s="17"/>
       <c r="B40" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75">
-      <c r="A41" s="18"/>
+    <row r="41" spans="1:2">
+      <c r="A41" s="17"/>
       <c r="B41" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="18.75">
-      <c r="A42" s="18"/>
+    <row r="42" spans="1:2" ht="18">
+      <c r="A42" s="17"/>
       <c r="B42" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="18.75">
-      <c r="A43" s="18"/>
+    <row r="43" spans="1:2" ht="18">
+      <c r="A43" s="17"/>
       <c r="B43" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75">
-      <c r="A44" s="18"/>
+    <row r="44" spans="1:2">
+      <c r="A44" s="17"/>
       <c r="B44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75">
-      <c r="A45" s="18"/>
+    <row r="45" spans="1:2">
+      <c r="A45" s="17"/>
       <c r="B45" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75">
-      <c r="A46" s="18"/>
+    <row r="46" spans="1:2">
+      <c r="A46" s="17"/>
       <c r="B46" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75">
-      <c r="A47" s="18"/>
+    <row r="47" spans="1:2">
+      <c r="A47" s="17"/>
       <c r="B47" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75">
-      <c r="A48" s="18"/>
+    <row r="48" spans="1:2">
+      <c r="A48" s="17"/>
       <c r="B48" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75">
-      <c r="A49" s="18"/>
+    <row r="49" spans="1:2">
+      <c r="A49" s="17"/>
       <c r="B49" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75">
-      <c r="A50" s="18"/>
+    <row r="50" spans="1:2">
+      <c r="A50" s="17"/>
       <c r="B50" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75">
-      <c r="A51" s="18"/>
+    <row r="51" spans="1:2">
+      <c r="A51" s="17"/>
       <c r="B51" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75">
-      <c r="A52" s="18"/>
+    <row r="52" spans="1:2">
+      <c r="A52" s="17"/>
       <c r="B52" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75">
-      <c r="A53" s="18"/>
+    <row r="53" spans="1:2">
+      <c r="A53" s="17"/>
       <c r="B53" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="18.75">
-      <c r="A54" s="18"/>
+    <row r="54" spans="1:2" ht="18">
+      <c r="A54" s="17"/>
       <c r="B54" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="18.75">
-      <c r="A55" s="18"/>
+    <row r="55" spans="1:2" ht="18">
+      <c r="A55" s="17"/>
       <c r="B55" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75">
-      <c r="A56" s="18"/>
+    <row r="56" spans="1:2">
+      <c r="A56" s="17"/>
       <c r="B56" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="18.75">
-      <c r="A57" s="18"/>
+    <row r="57" spans="1:2" ht="18">
+      <c r="A57" s="17"/>
       <c r="B57" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75">
-      <c r="A58" s="18" t="s">
+    <row r="58" spans="1:2">
+      <c r="A58" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75">
-      <c r="A59" s="18"/>
+    <row r="59" spans="1:2">
+      <c r="A59" s="17"/>
       <c r="B59" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75">
-      <c r="A60" s="18"/>
+    <row r="60" spans="1:2">
+      <c r="A60" s="17"/>
       <c r="B60" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75">
-      <c r="A61" s="18"/>
+    <row r="61" spans="1:2">
+      <c r="A61" s="17"/>
       <c r="B61" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75">
-      <c r="A62" s="18"/>
+    <row r="62" spans="1:2">
+      <c r="A62" s="17"/>
       <c r="B62" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75">
-      <c r="A63" s="18"/>
+    <row r="63" spans="1:2">
+      <c r="A63" s="17"/>
       <c r="B63" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75">
-      <c r="A64" s="18"/>
+    <row r="64" spans="1:2">
+      <c r="A64" s="17"/>
       <c r="B64" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75">
-      <c r="A65" s="18"/>
+    <row r="65" spans="1:2">
+      <c r="A65" s="17"/>
       <c r="B65" s="10" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75">
-      <c r="A66" s="18"/>
+    <row r="66" spans="1:2">
+      <c r="A66" s="17"/>
       <c r="B66" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75">
-      <c r="A67" s="18"/>
+    <row r="67" spans="1:2">
+      <c r="A67" s="17"/>
       <c r="B67" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75">
-      <c r="A68" s="18"/>
+    <row r="68" spans="1:2">
+      <c r="A68" s="17"/>
       <c r="B68" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75">
-      <c r="A69" s="18"/>
+    <row r="69" spans="1:2">
+      <c r="A69" s="17"/>
       <c r="B69" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="24">
+    <row r="70" spans="1:2" ht="23.25">
       <c r="A70" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75">
-      <c r="A71" s="16" t="s">
+    <row r="71" spans="1:2">
+      <c r="A71" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="16"/>
+      <c r="B71" s="18"/>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
@@ -1911,396 +1914,396 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="18.75">
-      <c r="A75" s="18" t="s">
+    <row r="75" spans="1:2" ht="18">
+      <c r="A75" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75">
-      <c r="A76" s="18"/>
+    <row r="76" spans="1:2">
+      <c r="A76" s="17"/>
       <c r="B76" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="18.75">
-      <c r="A77" s="18"/>
+    <row r="77" spans="1:2" ht="18">
+      <c r="A77" s="17"/>
       <c r="B77" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75">
-      <c r="A78" s="18"/>
+    <row r="78" spans="1:2">
+      <c r="A78" s="17"/>
       <c r="B78" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="18.75">
-      <c r="A79" s="18"/>
+    <row r="79" spans="1:2" ht="18">
+      <c r="A79" s="17"/>
       <c r="B79" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="18.75">
-      <c r="A80" s="18"/>
+    <row r="80" spans="1:2" ht="18">
+      <c r="A80" s="17"/>
       <c r="B80" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="18.75">
-      <c r="A81" s="18"/>
+    <row r="81" spans="1:2" ht="18">
+      <c r="A81" s="17"/>
       <c r="B81" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75">
-      <c r="A82" s="18"/>
+    <row r="82" spans="1:2">
+      <c r="A82" s="17"/>
       <c r="B82" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="18.75">
-      <c r="A83" s="18"/>
+    <row r="83" spans="1:2" ht="18">
+      <c r="A83" s="17"/>
       <c r="B83" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="18.75">
-      <c r="A84" s="18"/>
+    <row r="84" spans="1:2" ht="18">
+      <c r="A84" s="17"/>
       <c r="B84" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75">
-      <c r="A85" s="18"/>
+    <row r="85" spans="1:2">
+      <c r="A85" s="17"/>
       <c r="B85" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75">
-      <c r="A86" s="18"/>
+    <row r="86" spans="1:2">
+      <c r="A86" s="17"/>
       <c r="B86" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="18.75">
-      <c r="A87" s="18"/>
+    <row r="87" spans="1:2" ht="18">
+      <c r="A87" s="17"/>
       <c r="B87" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75">
-      <c r="A88" s="18" t="s">
+    <row r="88" spans="1:2">
+      <c r="A88" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75">
-      <c r="A89" s="18"/>
+    <row r="89" spans="1:2">
+      <c r="A89" s="17"/>
       <c r="B89" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75">
-      <c r="A90" s="18"/>
+    <row r="90" spans="1:2">
+      <c r="A90" s="17"/>
       <c r="B90" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75">
-      <c r="A91" s="18"/>
+    <row r="91" spans="1:2">
+      <c r="A91" s="17"/>
       <c r="B91" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75">
-      <c r="A92" s="18"/>
+    <row r="92" spans="1:2">
+      <c r="A92" s="17"/>
       <c r="B92" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="18.75">
-      <c r="A93" s="18" t="s">
+    <row r="93" spans="1:2" ht="18">
+      <c r="A93" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="18.75">
-      <c r="A94" s="18"/>
+    <row r="94" spans="1:2" ht="18">
+      <c r="A94" s="17"/>
       <c r="B94" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75">
-      <c r="A95" s="18"/>
+    <row r="95" spans="1:2">
+      <c r="A95" s="17"/>
       <c r="B95" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="18.75">
-      <c r="A96" s="18"/>
+    <row r="96" spans="1:2" ht="18">
+      <c r="A96" s="17"/>
       <c r="B96" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="18.75">
-      <c r="A97" s="18"/>
+    <row r="97" spans="1:2" ht="18">
+      <c r="A97" s="17"/>
       <c r="B97" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75">
-      <c r="A98" s="18"/>
+    <row r="98" spans="1:2">
+      <c r="A98" s="17"/>
       <c r="B98" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75">
-      <c r="A99" s="18"/>
+    <row r="99" spans="1:2">
+      <c r="A99" s="17"/>
       <c r="B99" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75">
-      <c r="A100" s="18"/>
+    <row r="100" spans="1:2">
+      <c r="A100" s="17"/>
       <c r="B100" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75">
-      <c r="A101" s="18"/>
+    <row r="101" spans="1:2">
+      <c r="A101" s="17"/>
       <c r="B101" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75">
-      <c r="A102" s="18"/>
+    <row r="102" spans="1:2">
+      <c r="A102" s="17"/>
       <c r="B102" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75">
-      <c r="A103" s="18"/>
+    <row r="103" spans="1:2">
+      <c r="A103" s="17"/>
       <c r="B103" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75">
-      <c r="A104" s="18"/>
+    <row r="104" spans="1:2">
+      <c r="A104" s="17"/>
       <c r="B104" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75">
-      <c r="A105" s="18"/>
+    <row r="105" spans="1:2">
+      <c r="A105" s="17"/>
       <c r="B105" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75">
-      <c r="A106" s="18"/>
+    <row r="106" spans="1:2">
+      <c r="A106" s="17"/>
       <c r="B106" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75">
-      <c r="A107" s="18"/>
+    <row r="107" spans="1:2">
+      <c r="A107" s="17"/>
       <c r="B107" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75">
-      <c r="A108" s="18"/>
+    <row r="108" spans="1:2">
+      <c r="A108" s="17"/>
       <c r="B108" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75">
-      <c r="A109" s="18"/>
+    <row r="109" spans="1:2">
+      <c r="A109" s="17"/>
       <c r="B109" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75">
-      <c r="A110" s="18"/>
+    <row r="110" spans="1:2">
+      <c r="A110" s="17"/>
       <c r="B110" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="18.75">
-      <c r="A111" s="18"/>
+    <row r="111" spans="1:2" ht="18">
+      <c r="A111" s="17"/>
       <c r="B111" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="18.75">
-      <c r="A112" s="18"/>
+    <row r="112" spans="1:2" ht="18">
+      <c r="A112" s="17"/>
       <c r="B112" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75">
-      <c r="A113" s="18"/>
+    <row r="113" spans="1:2">
+      <c r="A113" s="17"/>
       <c r="B113" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="18.75">
-      <c r="A114" s="18"/>
+    <row r="114" spans="1:2" ht="18">
+      <c r="A114" s="17"/>
       <c r="B114" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75">
-      <c r="A115" s="18" t="s">
+    <row r="115" spans="1:2">
+      <c r="A115" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75">
-      <c r="A116" s="18"/>
+    <row r="116" spans="1:2">
+      <c r="A116" s="17"/>
       <c r="B116" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75">
-      <c r="A117" s="18"/>
+    <row r="117" spans="1:2">
+      <c r="A117" s="17"/>
       <c r="B117" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15.75">
-      <c r="A118" s="18"/>
+    <row r="118" spans="1:2">
+      <c r="A118" s="17"/>
       <c r="B118" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15.75">
-      <c r="A119" s="18"/>
+    <row r="119" spans="1:2">
+      <c r="A119" s="17"/>
       <c r="B119" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15.75">
-      <c r="A120" s="18"/>
+    <row r="120" spans="1:2">
+      <c r="A120" s="17"/>
       <c r="B120" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15.75">
-      <c r="A121" s="18"/>
+    <row r="121" spans="1:2">
+      <c r="A121" s="17"/>
       <c r="B121" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15.75">
-      <c r="A122" s="18"/>
+    <row r="122" spans="1:2">
+      <c r="A122" s="17"/>
       <c r="B122" s="10" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15.75">
-      <c r="A123" s="18"/>
+    <row r="123" spans="1:2">
+      <c r="A123" s="17"/>
       <c r="B123" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="15.75">
-      <c r="A124" s="18"/>
+    <row r="124" spans="1:2">
+      <c r="A124" s="17"/>
       <c r="B124" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="15.75">
-      <c r="A125" s="18"/>
+    <row r="125" spans="1:2">
+      <c r="A125" s="17"/>
       <c r="B125" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="15.75">
-      <c r="A126" s="18"/>
+    <row r="126" spans="1:2">
+      <c r="A126" s="17"/>
       <c r="B126" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="15.75">
-      <c r="A127" s="18"/>
+    <row r="127" spans="1:2">
+      <c r="A127" s="17"/>
       <c r="B127" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15.75">
-      <c r="A128" s="18"/>
+    <row r="128" spans="1:2">
+      <c r="A128" s="17"/>
       <c r="B128" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="15.75">
-      <c r="A129" s="18"/>
+    <row r="129" spans="1:2">
+      <c r="A129" s="17"/>
       <c r="B129" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="24">
+    <row r="130" spans="1:2" ht="23.25">
       <c r="A130" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="15.75">
+    <row r="131" spans="1:2">
       <c r="A131" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B131" s="16"/>
-    </row>
-    <row r="132" spans="1:2" ht="15.75">
-      <c r="A132" s="18" t="s">
+      <c r="B131" s="18"/>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="15.75">
-      <c r="A133" s="18"/>
+    <row r="133" spans="1:2">
+      <c r="A133" s="17"/>
       <c r="B133" s="8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="15.75">
-      <c r="A134" s="18" t="s">
+    <row r="134" spans="1:2">
+      <c r="A134" s="17" t="s">
         <v>81</v>
       </c>
       <c r="B134" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="15.75">
-      <c r="A135" s="18"/>
+    <row r="135" spans="1:2">
+      <c r="A135" s="17"/>
       <c r="B135" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="15.75">
-      <c r="A136" s="18"/>
+    <row r="136" spans="1:2">
+      <c r="A136" s="17"/>
       <c r="B136" s="10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="15.75">
-      <c r="A137" s="18"/>
+    <row r="137" spans="1:2">
+      <c r="A137" s="17"/>
       <c r="B137" s="8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="15.75">
+    <row r="138" spans="1:2">
       <c r="A138" s="2" t="s">
         <v>5</v>
       </c>
@@ -2308,7 +2311,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="15.75">
+    <row r="139" spans="1:2">
       <c r="A139" s="2" t="s">
         <v>7</v>
       </c>
@@ -2316,7 +2319,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="26.25">
+    <row r="140" spans="1:2" ht="25.5">
       <c r="A140" s="2" t="s">
         <v>88</v>
       </c>
@@ -2324,121 +2327,121 @@
         <v>89</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="15.75">
-      <c r="A141" s="18" t="s">
+    <row r="141" spans="1:2">
+      <c r="A141" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="15.75">
-      <c r="A142" s="18"/>
+    <row r="142" spans="1:2">
+      <c r="A142" s="17"/>
       <c r="B142" s="10" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="15.75">
-      <c r="A143" s="18"/>
+    <row r="143" spans="1:2">
+      <c r="A143" s="17"/>
       <c r="B143" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="15.75">
-      <c r="A144" s="18"/>
+    <row r="144" spans="1:2">
+      <c r="A144" s="17"/>
       <c r="B144" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="15.75">
-      <c r="A145" s="18"/>
+    <row r="145" spans="1:2">
+      <c r="A145" s="17"/>
       <c r="B145" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="15.75">
-      <c r="A146" s="18"/>
+    <row r="146" spans="1:2">
+      <c r="A146" s="17"/>
       <c r="B146" s="10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="15.75">
-      <c r="A147" s="18"/>
+    <row r="147" spans="1:2">
+      <c r="A147" s="17"/>
       <c r="B147" s="8" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="18.75">
-      <c r="A148" s="18" t="s">
+    <row r="148" spans="1:2" ht="18">
+      <c r="A148" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="18.75">
-      <c r="A149" s="18"/>
+    <row r="149" spans="1:2" ht="18">
+      <c r="A149" s="17"/>
       <c r="B149" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="15.75">
-      <c r="A150" s="18"/>
+    <row r="150" spans="1:2">
+      <c r="A150" s="17"/>
       <c r="B150" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="18">
-      <c r="A151" s="18"/>
+    <row r="151" spans="1:2" ht="17.25">
+      <c r="A151" s="17"/>
       <c r="B151" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="18.75">
-      <c r="A152" s="18"/>
+    <row r="152" spans="1:2" ht="18">
+      <c r="A152" s="17"/>
       <c r="B152" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="15.75">
-      <c r="A153" s="18"/>
+    <row r="153" spans="1:2">
+      <c r="A153" s="17"/>
       <c r="B153" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="18.75">
-      <c r="A154" s="18"/>
+    <row r="154" spans="1:2" ht="18">
+      <c r="A154" s="17"/>
       <c r="B154" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="15.75">
-      <c r="A155" s="18" t="s">
+    <row r="155" spans="1:2">
+      <c r="A155" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="15.75">
-      <c r="A156" s="18"/>
+    <row r="156" spans="1:2">
+      <c r="A156" s="17"/>
       <c r="B156" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="15.75">
-      <c r="A157" s="18"/>
+    <row r="157" spans="1:2">
+      <c r="A157" s="17"/>
       <c r="B157" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="15.75">
-      <c r="A158" s="16" t="s">
+    <row r="158" spans="1:2">
+      <c r="A158" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B158" s="16"/>
-    </row>
-    <row r="159" spans="1:2" ht="15.75">
+      <c r="B158" s="18"/>
+    </row>
+    <row r="159" spans="1:2">
       <c r="A159" s="2" t="s">
         <v>100</v>
       </c>
@@ -2446,7 +2449,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="15.75">
+    <row r="160" spans="1:2">
       <c r="A160" s="2">
         <v>200</v>
       </c>
@@ -2454,7 +2457,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="15.75">
+    <row r="161" spans="1:2">
       <c r="A161" s="2">
         <v>201</v>
       </c>
@@ -2462,7 +2465,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="15.75">
+    <row r="162" spans="1:2">
       <c r="A162" s="2">
         <v>202</v>
       </c>
@@ -2470,7 +2473,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="15.75">
+    <row r="163" spans="1:2">
       <c r="A163" s="2">
         <v>203</v>
       </c>
@@ -2478,7 +2481,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="15.75">
+    <row r="164" spans="1:2">
       <c r="A164" s="2">
         <v>204</v>
       </c>
@@ -2486,7 +2489,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="15.75">
+    <row r="165" spans="1:2">
       <c r="A165" s="2">
         <v>205</v>
       </c>
@@ -2494,7 +2497,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="15.75">
+    <row r="166" spans="1:2">
       <c r="A166" s="2">
         <v>206</v>
       </c>
@@ -2502,7 +2505,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="15.75">
+    <row r="167" spans="1:2">
       <c r="A167" s="2">
         <v>207</v>
       </c>
@@ -2510,7 +2513,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="15.75">
+    <row r="168" spans="1:2">
       <c r="A168" s="2">
         <v>208</v>
       </c>
@@ -2518,7 +2521,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="15.75">
+    <row r="169" spans="1:2">
       <c r="A169" s="2">
         <v>209</v>
       </c>
@@ -2526,7 +2529,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="15.75">
+    <row r="170" spans="1:2">
       <c r="A170" s="2">
         <v>210</v>
       </c>
@@ -2534,7 +2537,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="15.75">
+    <row r="171" spans="1:2">
       <c r="A171" s="2">
         <v>211</v>
       </c>
@@ -2542,7 +2545,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="15.75">
+    <row r="172" spans="1:2">
       <c r="A172" s="2">
         <v>212</v>
       </c>
@@ -2550,7 +2553,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="15.75">
+    <row r="173" spans="1:2">
       <c r="A173" s="2">
         <v>213</v>
       </c>
@@ -2558,7 +2561,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="15.75">
+    <row r="174" spans="1:2">
       <c r="A174" s="2">
         <v>214</v>
       </c>
@@ -2566,7 +2569,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="15.75">
+    <row r="175" spans="1:2">
       <c r="A175" s="2">
         <v>215</v>
       </c>
@@ -2574,7 +2577,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="15.75">
+    <row r="176" spans="1:2">
       <c r="A176" s="2">
         <v>216</v>
       </c>
@@ -2582,7 +2585,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.75">
+    <row r="177" spans="1:3">
       <c r="A177" s="2">
         <v>217</v>
       </c>
@@ -2590,7 +2593,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75">
+    <row r="178" spans="1:3">
       <c r="A178" s="2">
         <v>218</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.75">
+    <row r="179" spans="1:3">
       <c r="A179" s="2">
         <v>219</v>
       </c>
@@ -2606,7 +2609,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.75">
+    <row r="180" spans="1:3">
       <c r="A180" s="2">
         <v>220</v>
       </c>
@@ -2614,7 +2617,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75">
+    <row r="181" spans="1:3">
       <c r="A181" s="2">
         <v>224</v>
       </c>
@@ -2622,7 +2625,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75">
+    <row r="182" spans="1:3">
       <c r="A182" s="2">
         <v>225</v>
       </c>
@@ -2630,7 +2633,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75">
+    <row r="183" spans="1:3">
       <c r="A183" s="2">
         <v>226</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75">
+    <row r="184" spans="1:3">
       <c r="A184" s="2">
         <v>300</v>
       </c>
@@ -2646,7 +2649,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75">
+    <row r="185" spans="1:3">
       <c r="A185" s="2">
         <v>301</v>
       </c>
@@ -2654,7 +2657,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75">
+    <row r="186" spans="1:3">
       <c r="A186" s="2">
         <v>302</v>
       </c>
@@ -2662,7 +2665,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75">
+    <row r="187" spans="1:3">
       <c r="A187" s="2">
         <v>400</v>
       </c>
@@ -2670,7 +2673,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75">
+    <row r="188" spans="1:3">
       <c r="A188" s="2">
         <v>402</v>
       </c>
@@ -2678,7 +2681,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75">
+    <row r="189" spans="1:3">
       <c r="A189" s="2">
         <v>401</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75">
+    <row r="190" spans="1:3">
       <c r="A190" s="2">
         <v>403</v>
       </c>
@@ -2694,14 +2697,14 @@
         <v>132</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75">
-      <c r="A191" s="17" t="s">
+    <row r="191" spans="1:3">
+      <c r="A191" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B191" s="17"/>
-      <c r="C191" s="17"/>
-    </row>
-    <row r="192" spans="1:3" ht="15.75">
+      <c r="B191" s="16"/>
+      <c r="C191" s="16"/>
+    </row>
+    <row r="192" spans="1:3">
       <c r="A192" s="15" t="s">
         <v>134</v>
       </c>
@@ -2712,7 +2715,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75">
+    <row r="193" spans="1:3">
       <c r="A193" s="15">
         <v>1</v>
       </c>
@@ -2723,7 +2726,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75">
+    <row r="194" spans="1:3">
       <c r="A194" s="15">
         <v>2</v>
       </c>
@@ -2734,7 +2737,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75">
+    <row r="195" spans="1:3">
       <c r="A195" s="15">
         <v>3</v>
       </c>
@@ -2745,7 +2748,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75">
+    <row r="196" spans="1:3">
       <c r="A196" s="15">
         <v>4</v>
       </c>
@@ -2756,7 +2759,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75">
+    <row r="197" spans="1:3">
       <c r="A197" s="15">
         <v>5</v>
       </c>
@@ -2767,7 +2770,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75">
+    <row r="198" spans="1:3">
       <c r="A198" s="15">
         <v>6</v>
       </c>
@@ -2778,7 +2781,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75">
+    <row r="199" spans="1:3">
       <c r="A199" s="15">
         <v>7</v>
       </c>
@@ -2789,7 +2792,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75">
+    <row r="200" spans="1:3">
       <c r="A200" s="15">
         <v>8</v>
       </c>
@@ -2800,7 +2803,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75">
+    <row r="201" spans="1:3">
       <c r="A201" s="15">
         <v>9</v>
       </c>
@@ -2811,7 +2814,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75">
+    <row r="202" spans="1:3">
       <c r="A202" s="15">
         <v>10</v>
       </c>
@@ -2822,7 +2825,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75">
+    <row r="203" spans="1:3">
       <c r="A203" s="15">
         <v>11</v>
       </c>
@@ -2833,7 +2836,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75">
+    <row r="204" spans="1:3">
       <c r="A204" s="15">
         <v>12</v>
       </c>
@@ -2844,7 +2847,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75">
+    <row r="205" spans="1:3">
       <c r="A205" s="15">
         <v>13</v>
       </c>
@@ -2855,7 +2858,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75">
+    <row r="206" spans="1:3">
       <c r="A206" s="15">
         <v>15</v>
       </c>
@@ -2866,7 +2869,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75">
+    <row r="207" spans="1:3">
       <c r="A207" s="15">
         <v>16</v>
       </c>
@@ -2877,7 +2880,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75">
+    <row r="208" spans="1:3">
       <c r="A208" s="15">
         <v>17</v>
       </c>
@@ -2888,7 +2891,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75">
+    <row r="209" spans="1:3">
       <c r="A209" s="15">
         <v>18</v>
       </c>
@@ -2899,7 +2902,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75">
+    <row r="210" spans="1:3">
       <c r="A210" s="15">
         <v>20</v>
       </c>
@@ -2910,7 +2913,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75">
+    <row r="211" spans="1:3">
       <c r="A211" s="15">
         <v>29</v>
       </c>
@@ -2921,7 +2924,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75">
+    <row r="212" spans="1:3">
       <c r="A212" s="15">
         <v>36</v>
       </c>
@@ -2932,7 +2935,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75">
+    <row r="213" spans="1:3">
       <c r="A213" s="15">
         <v>47</v>
       </c>
@@ -2943,7 +2946,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75">
+    <row r="214" spans="1:3">
       <c r="A214" s="15">
         <v>58</v>
       </c>
@@ -2954,7 +2957,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75">
+    <row r="215" spans="1:3">
       <c r="A215" s="15">
         <v>59</v>
       </c>
@@ -2965,7 +2968,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75">
+    <row r="216" spans="1:3">
       <c r="A216" s="15">
         <v>60</v>
       </c>
@@ -2976,7 +2979,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75">
+    <row r="217" spans="1:3">
       <c r="A217" s="15">
         <v>61</v>
       </c>
@@ -2987,7 +2990,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75">
+    <row r="218" spans="1:3">
       <c r="A218" s="15">
         <v>62</v>
       </c>
@@ -2998,7 +3001,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75">
+    <row r="219" spans="1:3">
       <c r="A219" s="15">
         <v>63</v>
       </c>
@@ -3009,7 +3012,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75">
+    <row r="220" spans="1:3">
       <c r="A220" s="15">
         <v>64</v>
       </c>
@@ -3020,7 +3023,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75">
+    <row r="221" spans="1:3">
       <c r="A221" s="15">
         <v>74</v>
       </c>
@@ -3031,7 +3034,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75">
+    <row r="222" spans="1:3">
       <c r="A222" s="15">
         <v>99</v>
       </c>
@@ -3042,7 +3045,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75">
+    <row r="223" spans="1:3">
       <c r="A223" s="15">
         <v>160</v>
       </c>
@@ -3053,7 +3056,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75">
+    <row r="224" spans="1:3">
       <c r="A224" s="15">
         <v>161</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75">
+    <row r="225" spans="1:3">
       <c r="A225" s="15">
         <v>162</v>
       </c>
@@ -3075,7 +3078,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.75">
+    <row r="226" spans="1:3">
       <c r="A226" s="15">
         <v>163</v>
       </c>
@@ -3086,7 +3089,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.75">
+    <row r="227" spans="1:3">
       <c r="A227" s="15">
         <v>164</v>
       </c>
@@ -3097,7 +3100,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.75">
+    <row r="228" spans="1:3">
       <c r="A228" s="15">
         <v>165</v>
       </c>
@@ -3108,7 +3111,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.75">
+    <row r="229" spans="1:3">
       <c r="A229" s="15">
         <v>166</v>
       </c>
@@ -3119,7 +3122,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.75">
+    <row r="230" spans="1:3">
       <c r="A230" s="15">
         <v>169</v>
       </c>
@@ -3130,7 +3133,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.75">
+    <row r="231" spans="1:3">
       <c r="A231" s="15">
         <v>172</v>
       </c>
@@ -3141,7 +3144,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.75">
+    <row r="232" spans="1:3">
       <c r="A232" s="15">
         <v>173</v>
       </c>
@@ -3152,7 +3155,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.75">
+    <row r="233" spans="1:3">
       <c r="A233" s="15">
         <v>174</v>
       </c>
@@ -3163,7 +3166,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.75">
+    <row r="234" spans="1:3">
       <c r="A234" s="15">
         <v>175</v>
       </c>
@@ -3174,7 +3177,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.75">
+    <row r="235" spans="1:3">
       <c r="A235" s="15">
         <v>176</v>
       </c>
@@ -3185,7 +3188,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.75">
+    <row r="236" spans="1:3">
       <c r="A236" s="15">
         <v>179</v>
       </c>
@@ -3196,7 +3199,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.75">
+    <row r="237" spans="1:3">
       <c r="A237" s="15">
         <v>294</v>
       </c>
@@ -3207,7 +3210,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.75">
+    <row r="238" spans="1:3">
       <c r="A238" s="15">
         <v>392</v>
       </c>
@@ -3218,7 +3221,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.75">
+    <row r="239" spans="1:3">
       <c r="A239" s="15">
         <v>394</v>
       </c>
@@ -3229,7 +3232,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.75">
+    <row r="240" spans="1:3">
       <c r="A240" s="15">
         <v>451</v>
       </c>
@@ -3240,7 +3243,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.75">
+    <row r="241" spans="1:3">
       <c r="A241" s="15">
         <v>453</v>
       </c>
@@ -3251,7 +3254,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.75">
+    <row r="242" spans="1:3">
       <c r="A242" s="15">
         <v>455</v>
       </c>
@@ -3264,6 +3267,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="A148:A154"/>
+    <mergeCell ref="A155:A157"/>
     <mergeCell ref="A191:C191"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A13"/>
@@ -3280,13 +3290,6 @@
     <mergeCell ref="A132:A133"/>
     <mergeCell ref="A134:A137"/>
     <mergeCell ref="A141:A147"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="A148:A154"/>
-    <mergeCell ref="A155:A157"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" tooltip="http://15.252.130.159:12056/api/v1/basic/key" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/docs/vendors/chemito/PMIDTC_CIPLAPIS.xlsx
+++ b/docs/vendors/chemito/PMIDTC_CIPLAPIS.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="11_25535FFD175E6FCFCB3D45214BAC33A9CAE27E25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14D7A69-8B06-4C34-9559-50EA4CAF0528}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="-14430" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -840,16 +840,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1457,10 +1457,10 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18"/>
+      <c r="B4" s="16"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
@@ -1487,7 +1487,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="18">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1495,25 +1495,25 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="17"/>
+      <c r="A9" s="18"/>
       <c r="B9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="17"/>
+      <c r="A10" s="18"/>
       <c r="B10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18">
-      <c r="A11" s="17"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -1521,13 +1521,13 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="17"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1535,43 +1535,43 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="18">
-      <c r="A15" s="17"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="17"/>
+      <c r="A16" s="18"/>
       <c r="B16" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="17"/>
+      <c r="A17" s="18"/>
       <c r="B17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="18">
-      <c r="A18" s="17"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="17"/>
+      <c r="A19" s="18"/>
       <c r="B19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18">
-      <c r="A20" s="17"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="7" t="s">
@@ -1579,13 +1579,13 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="17"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="17"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="8" t="s">
         <v>26</v>
       </c>
@@ -1596,10 +1596,10 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="18"/>
+      <c r="B25" s="16"/>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
@@ -1626,7 +1626,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" ht="18">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1634,37 +1634,37 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="17"/>
+      <c r="A30" s="18"/>
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="17"/>
+      <c r="A31" s="18"/>
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="17"/>
+      <c r="A32" s="18"/>
       <c r="B32" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="17"/>
+      <c r="A33" s="18"/>
       <c r="B33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="18">
-      <c r="A34" s="17"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="7" t="s">
@@ -1672,25 +1672,25 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="17"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="17"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="17"/>
+      <c r="A38" s="18"/>
       <c r="B38" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="18">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -1698,115 +1698,115 @@
       </c>
     </row>
     <row r="40" spans="1:2" ht="18">
-      <c r="A40" s="17"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="17"/>
+      <c r="A41" s="18"/>
       <c r="B41" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="18">
-      <c r="A42" s="17"/>
+      <c r="A42" s="18"/>
       <c r="B42" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="18">
-      <c r="A43" s="17"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="17"/>
+      <c r="A44" s="18"/>
       <c r="B44" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="17"/>
+      <c r="A45" s="18"/>
       <c r="B45" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="17"/>
+      <c r="A46" s="18"/>
       <c r="B46" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="17"/>
+      <c r="A47" s="18"/>
       <c r="B47" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="17"/>
+      <c r="A48" s="18"/>
       <c r="B48" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="17"/>
+      <c r="A49" s="18"/>
       <c r="B49" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="17"/>
+      <c r="A50" s="18"/>
       <c r="B50" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="17"/>
+      <c r="A51" s="18"/>
       <c r="B51" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="17"/>
+      <c r="A52" s="18"/>
       <c r="B52" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="17"/>
+      <c r="A53" s="18"/>
       <c r="B53" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="18">
-      <c r="A54" s="17"/>
+      <c r="A54" s="18"/>
       <c r="B54" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="18">
-      <c r="A55" s="17"/>
+      <c r="A55" s="18"/>
       <c r="B55" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="17"/>
+      <c r="A56" s="18"/>
       <c r="B56" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="18">
-      <c r="A57" s="17"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B58" s="7" t="s">
@@ -1814,67 +1814,67 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="17"/>
+      <c r="A59" s="18"/>
       <c r="B59" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="17"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="17"/>
+      <c r="A61" s="18"/>
       <c r="B61" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="17"/>
+      <c r="A62" s="18"/>
       <c r="B62" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="17"/>
+      <c r="A63" s="18"/>
       <c r="B63" s="10" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="17"/>
+      <c r="A64" s="18"/>
       <c r="B64" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="17"/>
+      <c r="A65" s="18"/>
       <c r="B65" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="17"/>
+      <c r="A66" s="18"/>
       <c r="B66" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="17"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="17"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="17"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="8" t="s">
         <v>26</v>
       </c>
@@ -1885,10 +1885,10 @@
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="18" t="s">
+      <c r="A71" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="18"/>
+      <c r="B71" s="16"/>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
@@ -1915,7 +1915,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" ht="18">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B75" s="5" t="s">
@@ -1923,79 +1923,79 @@
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="17"/>
+      <c r="A76" s="18"/>
       <c r="B76" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="18">
-      <c r="A77" s="17"/>
+      <c r="A77" s="18"/>
       <c r="B77" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="17"/>
+      <c r="A78" s="18"/>
       <c r="B78" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="18">
-      <c r="A79" s="17"/>
+      <c r="A79" s="18"/>
       <c r="B79" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="18">
-      <c r="A80" s="17"/>
+      <c r="A80" s="18"/>
       <c r="B80" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="18">
-      <c r="A81" s="17"/>
+      <c r="A81" s="18"/>
       <c r="B81" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="17"/>
+      <c r="A82" s="18"/>
       <c r="B82" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="18">
-      <c r="A83" s="17"/>
+      <c r="A83" s="18"/>
       <c r="B83" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="18">
-      <c r="A84" s="17"/>
+      <c r="A84" s="18"/>
       <c r="B84" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="17"/>
+      <c r="A85" s="18"/>
       <c r="B85" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="17"/>
+      <c r="A86" s="18"/>
       <c r="B86" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="18">
-      <c r="A87" s="17"/>
+      <c r="A87" s="18"/>
       <c r="B87" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="17" t="s">
+      <c r="A88" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B88" s="7" t="s">
@@ -2003,31 +2003,31 @@
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="17"/>
+      <c r="A89" s="18"/>
       <c r="B89" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="17"/>
+      <c r="A90" s="18"/>
       <c r="B90" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="17"/>
+      <c r="A91" s="18"/>
       <c r="B91" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="17"/>
+      <c r="A92" s="18"/>
       <c r="B92" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="18">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B93" s="5" t="s">
@@ -2035,133 +2035,133 @@
       </c>
     </row>
     <row r="94" spans="1:2" ht="18">
-      <c r="A94" s="17"/>
+      <c r="A94" s="18"/>
       <c r="B94" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="17"/>
+      <c r="A95" s="18"/>
       <c r="B95" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="18">
-      <c r="A96" s="17"/>
+      <c r="A96" s="18"/>
       <c r="B96" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="18">
-      <c r="A97" s="17"/>
+      <c r="A97" s="18"/>
       <c r="B97" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="17"/>
+      <c r="A98" s="18"/>
       <c r="B98" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="17"/>
+      <c r="A99" s="18"/>
       <c r="B99" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="17"/>
+      <c r="A100" s="18"/>
       <c r="B100" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="17"/>
+      <c r="A101" s="18"/>
       <c r="B101" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="17"/>
+      <c r="A102" s="18"/>
       <c r="B102" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="17"/>
+      <c r="A103" s="18"/>
       <c r="B103" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="17"/>
+      <c r="A104" s="18"/>
       <c r="B104" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="17"/>
+      <c r="A105" s="18"/>
       <c r="B105" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="17"/>
+      <c r="A106" s="18"/>
       <c r="B106" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="17"/>
+      <c r="A107" s="18"/>
       <c r="B107" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="17"/>
+      <c r="A108" s="18"/>
       <c r="B108" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="17"/>
+      <c r="A109" s="18"/>
       <c r="B109" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="17"/>
+      <c r="A110" s="18"/>
       <c r="B110" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="18">
-      <c r="A111" s="17"/>
+      <c r="A111" s="18"/>
       <c r="B111" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="18">
-      <c r="A112" s="17"/>
+      <c r="A112" s="18"/>
       <c r="B112" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="17"/>
+      <c r="A113" s="18"/>
       <c r="B113" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="18">
-      <c r="A114" s="17"/>
+      <c r="A114" s="18"/>
       <c r="B114" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B115" s="7" t="s">
@@ -2169,85 +2169,85 @@
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="17"/>
+      <c r="A116" s="18"/>
       <c r="B116" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="17"/>
+      <c r="A117" s="18"/>
       <c r="B117" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="17"/>
+      <c r="A118" s="18"/>
       <c r="B118" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="17"/>
+      <c r="A119" s="18"/>
       <c r="B119" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="17"/>
+      <c r="A120" s="18"/>
       <c r="B120" s="10" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="17"/>
+      <c r="A121" s="18"/>
       <c r="B121" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="17"/>
+      <c r="A122" s="18"/>
       <c r="B122" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="17"/>
+      <c r="A123" s="18"/>
       <c r="B123" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="17"/>
+      <c r="A124" s="18"/>
       <c r="B124" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="17"/>
+      <c r="A125" s="18"/>
       <c r="B125" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="17"/>
+      <c r="A126" s="18"/>
       <c r="B126" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="17"/>
+      <c r="A127" s="18"/>
       <c r="B127" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="17"/>
+      <c r="A128" s="18"/>
       <c r="B128" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="17"/>
+      <c r="A129" s="18"/>
       <c r="B129" s="8" t="s">
         <v>26</v>
       </c>
@@ -2258,13 +2258,13 @@
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="19" t="s">
+      <c r="A131" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B131" s="18"/>
+      <c r="B131" s="16"/>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="17" t="s">
+      <c r="A132" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B132" s="7" t="s">
@@ -2272,13 +2272,13 @@
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="17"/>
+      <c r="A133" s="18"/>
       <c r="B133" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="17" t="s">
+      <c r="A134" s="18" t="s">
         <v>81</v>
       </c>
       <c r="B134" t="s">
@@ -2286,19 +2286,19 @@
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="17"/>
+      <c r="A135" s="18"/>
       <c r="B135" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="17"/>
+      <c r="A136" s="18"/>
       <c r="B136" s="10" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="17"/>
+      <c r="A137" s="18"/>
       <c r="B137" s="8" t="s">
         <v>85</v>
       </c>
@@ -2328,7 +2328,7 @@
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="17" t="s">
+      <c r="A141" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B141" s="7" t="s">
@@ -2336,43 +2336,43 @@
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="17"/>
+      <c r="A142" s="18"/>
       <c r="B142" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="17"/>
+      <c r="A143" s="18"/>
       <c r="B143" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="17"/>
+      <c r="A144" s="18"/>
       <c r="B144" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="17"/>
+      <c r="A145" s="18"/>
       <c r="B145" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="17"/>
+      <c r="A146" s="18"/>
       <c r="B146" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="17"/>
+      <c r="A147" s="18"/>
       <c r="B147" s="8" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="18">
-      <c r="A148" s="17" t="s">
+      <c r="A148" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B148" s="5" t="s">
@@ -2380,43 +2380,43 @@
       </c>
     </row>
     <row r="149" spans="1:2" ht="18">
-      <c r="A149" s="17"/>
+      <c r="A149" s="18"/>
       <c r="B149" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="17"/>
+      <c r="A150" s="18"/>
       <c r="B150" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="17.25">
-      <c r="A151" s="17"/>
+      <c r="A151" s="18"/>
       <c r="B151" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="18">
-      <c r="A152" s="17"/>
+      <c r="A152" s="18"/>
       <c r="B152" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="17"/>
+      <c r="A153" s="18"/>
       <c r="B153" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="18">
-      <c r="A154" s="17"/>
+      <c r="A154" s="18"/>
       <c r="B154" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="17" t="s">
+      <c r="A155" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B155" s="7" t="s">
@@ -2424,22 +2424,22 @@
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="17"/>
+      <c r="A156" s="18"/>
       <c r="B156" s="10" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="17"/>
+      <c r="A157" s="18"/>
       <c r="B157" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="18" t="s">
+      <c r="A158" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B158" s="18"/>
+      <c r="B158" s="16"/>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2" t="s">
@@ -2698,11 +2698,11 @@
       </c>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="16" t="s">
+      <c r="A191" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B191" s="16"/>
-      <c r="C191" s="16"/>
+      <c r="B191" s="19"/>
+      <c r="C191" s="19"/>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="15" t="s">
@@ -3267,13 +3267,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="A148:A154"/>
-    <mergeCell ref="A155:A157"/>
     <mergeCell ref="A191:C191"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A13"/>
@@ -3290,6 +3283,13 @@
     <mergeCell ref="A132:A133"/>
     <mergeCell ref="A134:A137"/>
     <mergeCell ref="A141:A147"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="A148:A154"/>
+    <mergeCell ref="A155:A157"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" tooltip="http://15.252.130.159:12056/api/v1/basic/key" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
